--- a/data/trans_dic/P59A-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P59A-Clase-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que vive actualmente en pareja</t>
+          <t>Población que vive actualmente en pareja (tasa de respuesta: 98,5%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>15,04; 28,85</t>
+          <t>14,76; 29,5</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>16,04; 30,96</t>
+          <t>15,99; 31,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9,27; 20,0</t>
+          <t>9,09; 19,96</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>16,44; 29,84</t>
+          <t>16,93; 29,58</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>10,97; 24,79</t>
+          <t>10,91; 25,05</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>15,54; 32,82</t>
+          <t>16,26; 34,02</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,62; 24,85</t>
+          <t>11,55; 24,36</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>15,93; 26,03</t>
+          <t>16,15; 26,02</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>15,06; 25,17</t>
+          <t>14,72; 24,47</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>18,25; 29,63</t>
+          <t>18,54; 29,45</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>11,57; 19,86</t>
+          <t>11,6; 19,91</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>18,11; 25,74</t>
+          <t>18,01; 25,71</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>10,17; 23,39</t>
+          <t>10,24; 22,4</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>9,78; 24,63</t>
+          <t>10,1; 24,29</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>25,98; 43,95</t>
+          <t>26,92; 44,49</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9,19; 21,12</t>
+          <t>8,83; 21,34</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>17,37; 30,27</t>
+          <t>16,82; 31,19</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,02; 31,82</t>
+          <t>15,09; 30,51</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,34; 25,21</t>
+          <t>12,45; 25,59</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>16,07; 27,51</t>
+          <t>16,17; 27,69</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>15,85; 25,16</t>
+          <t>15,57; 25,22</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>13,31; 24,52</t>
+          <t>13,69; 24,43</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>20,47; 31,15</t>
+          <t>20,32; 30,58</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>13,79; 21,94</t>
+          <t>13,66; 21,39</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>15,16; 28,94</t>
+          <t>14,91; 28,22</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>16,79; 29,75</t>
+          <t>17,17; 29,75</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>13,38; 27,11</t>
+          <t>13,29; 26,72</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>17,11; 32,52</t>
+          <t>17,11; 32,02</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,08; 19,59</t>
+          <t>2,05; 17,75</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>12,42; 27,87</t>
+          <t>11,9; 27,75</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9,09; 29,63</t>
+          <t>9,58; 29,16</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6,35; 19,62</t>
+          <t>6,43; 19,43</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>13,12; 25,16</t>
+          <t>12,86; 23,93</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>16,78; 26,8</t>
+          <t>16,54; 26,43</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>13,71; 24,79</t>
+          <t>13,94; 24,79</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>14,81; 26,16</t>
+          <t>14,79; 26,44</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>12,6; 19,92</t>
+          <t>12,61; 20,12</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>14,88; 23,09</t>
+          <t>14,65; 22,78</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>19,33; 27,4</t>
+          <t>19,07; 27,28</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>15,23; 24,09</t>
+          <t>15,26; 24,22</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>8,14; 15,77</t>
+          <t>8,59; 16,03</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>17,82; 26,99</t>
+          <t>17,91; 27,07</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>16,31; 24,6</t>
+          <t>16,24; 24,06</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>13,97; 21,46</t>
+          <t>14,17; 21,65</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>11,72; 17,16</t>
+          <t>11,72; 17,38</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>17,02; 23,3</t>
+          <t>17,4; 23,77</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>18,72; 24,4</t>
+          <t>18,72; 24,41</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>15,72; 21,66</t>
+          <t>15,76; 22,02</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>9,75; 21,12</t>
+          <t>9,31; 21,23</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>10,95; 20,46</t>
+          <t>10,54; 20,5</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13,18; 23,03</t>
+          <t>13,24; 22,54</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10,35; 21,02</t>
+          <t>9,97; 20,58</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>8,89; 18,42</t>
+          <t>8,85; 19,11</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,81; 18,86</t>
+          <t>9,85; 18,46</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,72; 19,82</t>
+          <t>12,05; 20,46</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>5,29; 13,29</t>
+          <t>5,73; 13,3</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>9,98; 18,02</t>
+          <t>10,54; 18,13</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>11,18; 17,87</t>
+          <t>11,18; 17,96</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>13,53; 19,78</t>
+          <t>13,7; 19,95</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>7,85; 14,59</t>
+          <t>7,56; 14,66</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,48</t>
+          <t>0,0; 1,69</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 0,75</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,15; 5,1</t>
+          <t>1,05; 5,0</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,1; 8,01</t>
+          <t>0,2; 7,46</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1,6; 4,76</t>
+          <t>1,78; 4,89</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2,47; 6,24</t>
+          <t>2,53; 6,15</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3,73; 7,75</t>
+          <t>3,68; 7,95</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3,59; 9,41</t>
+          <t>3,4; 8,84</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1,21; 3,39</t>
+          <t>1,25; 3,28</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1,61; 4,0</t>
+          <t>1,62; 4,14</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3,17; 6,11</t>
+          <t>3,08; 6,06</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>2,81; 7,51</t>
+          <t>2,67; 6,67</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>11,66; 15,56</t>
+          <t>11,52; 15,54</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>13,55; 17,6</t>
+          <t>13,49; 17,67</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>15,63; 19,59</t>
+          <t>15,47; 19,73</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>13,83; 18,66</t>
+          <t>13,9; 18,58</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>8,51; 11,9</t>
+          <t>8,64; 11,93</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>12,52; 16,27</t>
+          <t>12,27; 16,28</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>12,48; 16,06</t>
+          <t>12,44; 16,05</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>10,93; 14,72</t>
+          <t>11,21; 14,96</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>10,56; 13,19</t>
+          <t>10,53; 13,24</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>13,44; 16,29</t>
+          <t>13,43; 16,27</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>14,56; 17,38</t>
+          <t>14,42; 17,06</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>13,1; 16,01</t>
+          <t>13,05; 15,98</t>
         </is>
       </c>
     </row>
@@ -1669,7 +1669,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que vive actualmente en pareja</t>
+          <t>Población que vive actualmente en pareja (tasa de respuesta: 98,5%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>21861; 41920</t>
+          <t>21448; 42861</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>24492; 47286</t>
+          <t>24420; 47345</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>17338; 37389</t>
+          <t>16988; 37326</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>33083; 60055</t>
+          <t>34071; 59521</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>13610; 30759</t>
+          <t>13539; 31081</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>17951; 37916</t>
+          <t>18778; 39296</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>17981; 38445</t>
+          <t>17861; 37679</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>34062; 55680</t>
+          <t>34535; 55638</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>40561; 67811</t>
+          <t>39649; 65914</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>48952; 79468</t>
+          <t>49728; 78999</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>39514; 67851</t>
+          <t>39640; 68038</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>75170; 106855</t>
+          <t>74753; 106715</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>12480; 28702</t>
+          <t>12573; 27495</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>13123; 33059</t>
+          <t>13564; 32602</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>33435; 56572</t>
+          <t>34651; 57257</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>17903; 41132</t>
+          <t>17201; 41549</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>28554; 49754</t>
+          <t>27654; 51261</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>17668; 37441</t>
+          <t>17759; 35894</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>18889; 38575</t>
+          <t>19048; 39159</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>29003; 49668</t>
+          <t>29195; 49992</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>45520; 72246</t>
+          <t>44695; 72413</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>33535; 61772</t>
+          <t>34478; 61539</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>57662; 87759</t>
+          <t>57243; 86143</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>51754; 82335</t>
+          <t>51254; 80280</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>24126; 46069</t>
+          <t>23732; 44916</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>32586; 57759</t>
+          <t>33336; 57741</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>20816; 42187</t>
+          <t>20683; 41578</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>31156; 59236</t>
+          <t>31166; 58317</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>940; 8876</t>
+          <t>928; 8040</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>12229; 27455</t>
+          <t>11718; 27330</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>6202; 20228</t>
+          <t>6538; 19908</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>4878; 15070</t>
+          <t>4942; 14924</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>26817; 51449</t>
+          <t>26296; 48930</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>49112; 78431</t>
+          <t>48392; 77335</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>30696; 55504</t>
+          <t>31202; 55500</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>38351; 67748</t>
+          <t>38292; 68465</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>51655; 81656</t>
+          <t>51689; 82478</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>62070; 96291</t>
+          <t>61116; 95024</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>79782; 113112</t>
+          <t>78737; 112629</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>76127; 120369</t>
+          <t>76236; 121044</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>25161; 48749</t>
+          <t>26565; 49560</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>57508; 87129</t>
+          <t>57803; 87379</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>67857; 102341</t>
+          <t>67581; 100110</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>53088; 81538</t>
+          <t>53829; 82232</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>84290; 123384</t>
+          <t>84272; 124965</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>125952; 172395</t>
+          <t>128721; 175893</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>155141; 202238</t>
+          <t>155197; 202344</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>138294; 190511</t>
+          <t>138588; 193727</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>15747; 34115</t>
+          <t>15034; 34287</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>24458; 45699</t>
+          <t>23546; 45784</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>38835; 67883</t>
+          <t>39016; 66437</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>26663; 54150</t>
+          <t>25682; 53018</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>17513; 36272</t>
+          <t>17432; 37639</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>27719; 53281</t>
+          <t>27816; 52154</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>37106; 62757</t>
+          <t>38145; 64785</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>22256; 55908</t>
+          <t>24103; 55920</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>35787; 64612</t>
+          <t>37776; 64986</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>56567; 90379</t>
+          <t>56569; 90813</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>82709; 120880</t>
+          <t>83741; 121954</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>53210; 98945</t>
+          <t>51287; 99407</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 4257</t>
+          <t>0; 4861</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 1926</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3191; 14165</t>
+          <t>2905; 13876</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>239; 18918</t>
+          <t>471; 17624</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>8656; 25778</t>
+          <t>9655; 26466</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>11996; 30300</t>
+          <t>12285; 29886</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>17870; 37120</t>
+          <t>17649; 38091</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>15315; 40168</t>
+          <t>14511; 37727</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>10036; 28099</t>
+          <t>10353; 27173</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>11966; 29684</t>
+          <t>12070; 30725</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>23970; 46229</t>
+          <t>23302; 45867</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>18611; 49793</t>
+          <t>17728; 44240</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>149905; 200056</t>
+          <t>148176; 199818</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>186741; 242547</t>
+          <t>185926; 243598</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>227607; 285309</t>
+          <t>225352; 287259</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>217373; 293236</t>
+          <t>218459; 292100</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>117584; 164306</t>
+          <t>119396; 164758</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>178142; 231558</t>
+          <t>174627; 231653</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>198142; 254976</t>
+          <t>197549; 254781</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>185648; 250084</t>
+          <t>190364; 254159</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>281515; 351900</t>
+          <t>280883; 352983</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>376419; 456231</t>
+          <t>376100; 455811</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>443195; 529112</t>
+          <t>439060; 519329</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>428284; 523453</t>
+          <t>426618; 522568</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P59A-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P59A-Clase-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>22,56%</t>
+          <t>21,92%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>20,53%</t>
+          <t>20,07%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>21,52%</t>
+          <t>20,96%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>14,76; 29,5</t>
+          <t>14,8; 29,21</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>15,99; 31,0</t>
+          <t>17,09; 31,49</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9,09; 19,96</t>
+          <t>9,16; 19,78</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>16,93; 29,58</t>
+          <t>15,89; 28,72</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>10,91; 25,05</t>
+          <t>10,89; 24,84</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,26; 34,02</t>
+          <t>16,32; 34,31</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,55; 24,36</t>
+          <t>11,64; 24,97</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>16,15; 26,02</t>
+          <t>16,04; 25,47</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>14,72; 24,47</t>
+          <t>14,31; 24,36</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>18,54; 29,45</t>
+          <t>18,16; 30,07</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>11,6; 19,91</t>
+          <t>11,61; 19,89</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>18,01; 25,71</t>
+          <t>17,44; 24,85</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>15,78%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>21,08%</t>
+          <t>21,01%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>18,33%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>10,24; 22,4</t>
+          <t>10,11; 23,06</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>10,1; 24,29</t>
+          <t>9,64; 24,08</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>26,92; 44,49</t>
+          <t>26,67; 44,18</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8,83; 21,34</t>
+          <t>10,65; 22,81</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>16,82; 31,19</t>
+          <t>17,88; 30,9</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,09; 30,51</t>
+          <t>15,33; 31,37</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,45; 25,59</t>
+          <t>12,26; 26,03</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>16,17; 27,69</t>
+          <t>16,16; 27,17</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>15,57; 25,22</t>
+          <t>15,76; 25,15</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>13,69; 24,43</t>
+          <t>14,06; 24,83</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>20,32; 30,58</t>
+          <t>20,8; 31,05</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>13,66; 21,39</t>
+          <t>14,48; 22,81</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>23,41%</t>
+          <t>22,92%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>19,92%</t>
+          <t>19,68%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>14,91; 28,22</t>
+          <t>14,58; 28,57</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>17,17; 29,75</t>
+          <t>17,09; 30,22</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>13,29; 26,72</t>
+          <t>13,32; 26,19</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>17,11; 32,02</t>
+          <t>16,3; 30,86</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,05; 17,75</t>
+          <t>2,09; 18,24</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>11,9; 27,75</t>
+          <t>12,08; 28,91</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9,58; 29,16</t>
+          <t>8,99; 28,83</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6,43; 19,43</t>
+          <t>6,85; 19,73</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>12,86; 23,93</t>
+          <t>12,69; 24,35</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>16,54; 26,43</t>
+          <t>17,1; 27,06</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>13,94; 24,79</t>
+          <t>13,63; 24,27</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>14,79; 26,44</t>
+          <t>14,93; 26,41</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>19,23%</t>
+          <t>19,99%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>18,51%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>18,54%</t>
+          <t>19,33%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>12,61; 20,12</t>
+          <t>12,68; 19,69</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>14,65; 22,78</t>
+          <t>14,79; 22,69</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>19,07; 27,28</t>
+          <t>18,64; 27,38</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>15,26; 24,22</t>
+          <t>15,9; 24,68</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>8,59; 16,03</t>
+          <t>8,48; 15,98</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>17,91; 27,07</t>
+          <t>17,17; 27,08</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>16,24; 24,06</t>
+          <t>15,98; 24,11</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>14,17; 21,65</t>
+          <t>15,06; 22,98</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>11,72; 17,38</t>
+          <t>11,74; 16,85</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>17,4; 23,77</t>
+          <t>16,96; 23,09</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>18,72; 24,41</t>
+          <t>18,94; 24,22</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>15,76; 22,02</t>
+          <t>16,67; 22,27</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>12,49%</t>
         </is>
       </c>
     </row>
@@ -1277,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>9,31; 21,23</t>
+          <t>8,81; 21,55</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>10,54; 20,5</t>
+          <t>10,16; 19,92</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13,24; 22,54</t>
+          <t>13,61; 23,12</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9,97; 20,58</t>
+          <t>9,07; 19,34</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>8,85; 19,11</t>
+          <t>9,27; 19,79</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,85; 18,46</t>
+          <t>9,64; 18,83</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,05; 20,46</t>
+          <t>11,86; 20,02</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>5,73; 13,3</t>
+          <t>8,94; 14,81</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>10,54; 18,13</t>
+          <t>10,24; 17,99</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>11,18; 17,96</t>
+          <t>11,28; 17,39</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>13,7; 19,95</t>
+          <t>13,51; 19,93</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>7,56; 14,66</t>
+          <t>10,22; 15,64</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,49%</t>
         </is>
       </c>
     </row>
@@ -1417,7 +1417,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,69</t>
+          <t>0,0; 1,5</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1427,52 +1427,52 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,05; 5,0</t>
+          <t>1,05; 5,23</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,2; 7,46</t>
+          <t>0,74; 8,2</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1,78; 4,89</t>
+          <t>1,68; 4,68</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2,53; 6,15</t>
+          <t>2,48; 6,24</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3,68; 7,95</t>
+          <t>3,57; 7,76</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3,4; 8,84</t>
+          <t>3,34; 8,12</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1,25; 3,28</t>
+          <t>1,2; 3,18</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1,62; 4,14</t>
+          <t>1,63; 4,16</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3,08; 6,06</t>
+          <t>3,14; 6,23</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>2,67; 6,67</t>
+          <t>2,66; 6,94</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>16,51%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>15,09%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>11,52; 15,54</t>
+          <t>11,77; 15,64</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>13,49; 17,67</t>
+          <t>13,54; 17,73</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>15,47; 19,73</t>
+          <t>15,66; 19,62</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>13,9; 18,58</t>
+          <t>14,32; 18,95</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>8,64; 11,93</t>
+          <t>8,66; 12,1</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>12,27; 16,28</t>
+          <t>12,3; 16,23</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>12,44; 16,05</t>
+          <t>12,43; 15,83</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>11,21; 14,96</t>
+          <t>12,18; 15,35</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>10,53; 13,24</t>
+          <t>10,62; 13,18</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>13,43; 16,27</t>
+          <t>13,33; 16,19</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>14,42; 17,06</t>
+          <t>14,52; 17,23</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>13,05; 15,98</t>
+          <t>13,71; 16,45</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>45408</t>
+          <t>47020</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>43914</t>
+          <t>46763</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>89322</t>
+          <t>93783</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>21448; 42861</t>
+          <t>21499; 42441</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>24420; 47345</t>
+          <t>26103; 48091</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>16988; 37326</t>
+          <t>17124; 36979</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>34071; 59521</t>
+          <t>34082; 61612</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>13539; 31081</t>
+          <t>13513; 30821</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>18778; 39296</t>
+          <t>18855; 39633</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>17861; 37679</t>
+          <t>18011; 38628</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>34535; 55638</t>
+          <t>37364; 59330</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>39649; 65914</t>
+          <t>38560; 65615</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>49728; 78999</t>
+          <t>48712; 80659</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>39640; 68038</t>
+          <t>39684; 67944</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>74753; 106715</t>
+          <t>78058; 111209</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>27553</t>
+          <t>32380</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>38061</t>
+          <t>41057</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>65614</t>
+          <t>73438</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>12573; 27495</t>
+          <t>12408; 28297</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>13564; 32602</t>
+          <t>12934; 32326</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>34651; 57257</t>
+          <t>34332; 56863</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>17201; 41549</t>
+          <t>21864; 46809</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>27654; 51261</t>
+          <t>29386; 50795</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>17759; 35894</t>
+          <t>18040; 36906</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>19048; 39159</t>
+          <t>18764; 39827</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>29195; 49992</t>
+          <t>31577; 53086</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>44695; 72413</t>
+          <t>45243; 72201</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>34478; 61539</t>
+          <t>35413; 62557</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>57243; 86143</t>
+          <t>58597; 87484</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>51254; 80280</t>
+          <t>58014; 91396</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>42630</t>
+          <t>45649</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>8949</t>
+          <t>10561</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>51579</t>
+          <t>56209</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>23732; 44916</t>
+          <t>23210; 45475</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>33336; 57741</t>
+          <t>33178; 58671</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>20683; 41578</t>
+          <t>20731; 40764</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>31166; 58317</t>
+          <t>32467; 61457</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>928; 8040</t>
+          <t>949; 8261</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>11718; 27330</t>
+          <t>11897; 28478</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>6538; 19908</t>
+          <t>6134; 19678</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>4942; 14924</t>
+          <t>5924; 17055</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>26296; 48930</t>
+          <t>25957; 49795</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>48392; 77335</t>
+          <t>50049; 79194</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>31202; 55500</t>
+          <t>30523; 54333</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>38292; 68465</t>
+          <t>42644; 75411</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>96118</t>
+          <t>106873</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>66993</t>
+          <t>78547</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>163111</t>
+          <t>185420</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>51689; 82478</t>
+          <t>51983; 80709</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>61116; 95024</t>
+          <t>61709; 94646</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>78737; 112629</t>
+          <t>76964; 113037</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>76236; 121044</t>
+          <t>84989; 131930</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>26565; 49560</t>
+          <t>26199; 49393</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>57803; 87379</t>
+          <t>55432; 87398</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>67581; 100110</t>
+          <t>66474; 100320</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>53829; 82232</t>
+          <t>63911; 97552</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>84272; 124965</t>
+          <t>84436; 121132</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>128721; 175893</t>
+          <t>125450; 170855</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>155197; 202344</t>
+          <t>157026; 200710</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>138588; 193727</t>
+          <t>159818; 213583</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>37352</t>
+          <t>40483</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>40546</t>
+          <t>46770</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>77898</t>
+          <t>87253</t>
         </is>
       </c>
     </row>
@@ -2759,69 +2759,69 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>15034; 34287</t>
+          <t>14225; 34798</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>23546; 45784</t>
+          <t>22685; 44484</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>39016; 66437</t>
+          <t>40109; 68147</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>25682; 53018</t>
+          <t>27479; 58616</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>17432; 37639</t>
+          <t>18258; 38977</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>27816; 52154</t>
+          <t>27242; 53176</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>38145; 64785</t>
+          <t>37562; 63393</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>24103; 55920</t>
+          <t>35344; 58578</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>37776; 64986</t>
+          <t>36719; 64504</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>56569; 90813</t>
+          <t>57036; 87935</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>83741; 121954</t>
+          <t>82558; 121816</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>51287; 99407</t>
+          <t>71433; 109255</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5070</t>
+          <t>6464</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>24075</t>
+          <t>25181</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>29145</t>
+          <t>31645</t>
         </is>
       </c>
     </row>
@@ -2967,7 +2967,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 4861</t>
+          <t>0; 4313</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -2977,52 +2977,52 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2905; 13876</t>
+          <t>2910; 14525</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>471; 17624</t>
+          <t>1714; 19109</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>9655; 26466</t>
+          <t>9089; 25329</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>12285; 29886</t>
+          <t>12043; 30309</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>17649; 38091</t>
+          <t>17110; 37198</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>14511; 37727</t>
+          <t>15785; 38364</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>10353; 27173</t>
+          <t>9954; 26333</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>12070; 30725</t>
+          <t>12121; 30936</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>23302; 45867</t>
+          <t>23750; 47112</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>17728; 44240</t>
+          <t>18794; 48938</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>254131</t>
+          <t>278869</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>222539</t>
+          <t>248879</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>476669</t>
+          <t>527748</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>148176; 199818</t>
+          <t>151364; 201099</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>185926; 243598</t>
+          <t>186708; 244441</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>225352; 287259</t>
+          <t>228063; 285689</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>218459; 292100</t>
+          <t>241942; 320134</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>119396; 164758</t>
+          <t>119674; 167116</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>174627; 231653</t>
+          <t>174989; 230853</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>197549; 254781</t>
+          <t>197404; 251335</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>190364; 254159</t>
+          <t>220115; 277465</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>280883; 352983</t>
+          <t>283211; 351607</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>376100; 455811</t>
+          <t>373541; 453448</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>439060; 519329</t>
+          <t>442040; 524427</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>426618; 522568</t>
+          <t>479357; 575084</t>
         </is>
       </c>
     </row>
